--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126301609</v>
       </c>
       <c r="B2" t="n">
-        <v>57641</v>
+        <v>57645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126301609</v>
       </c>
       <c r="B2" t="n">
-        <v>57645</v>
+        <v>57646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,337 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132110046</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57904</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ö.Sund N.strandnära skog, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>363552</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6612912</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132110059</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57920</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ö.Sund N.strandnära skog, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>363552</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6612912</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132110040</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57828</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ö.Sund N.strandnära skog, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>363552</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6612912</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>132110046</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132110059</v>
       </c>
       <c r="B4" t="n">
-        <v>57920</v>
+        <v>57925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>132110040</v>
       </c>
       <c r="B5" t="n">
-        <v>57828</v>
+        <v>57833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>132110046</v>
       </c>
       <c r="B3" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132110059</v>
+        <v>132110040</v>
       </c>
       <c r="B4" t="n">
-        <v>57925</v>
+        <v>57835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -927,14 +927,10 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1006,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132110040</v>
+        <v>132110059</v>
       </c>
       <c r="B5" t="n">
-        <v>57833</v>
+        <v>57927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,16 +1013,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1040,10 +1036,14 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132110040</v>
+        <v>132110059</v>
       </c>
       <c r="B4" t="n">
-        <v>57835</v>
+        <v>57927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -927,10 +927,14 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1002,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132110059</v>
+        <v>132110040</v>
       </c>
       <c r="B5" t="n">
-        <v>57927</v>
+        <v>57835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,16 +1017,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1036,14 +1040,10 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132110059</v>
+        <v>132110040</v>
       </c>
       <c r="B4" t="n">
-        <v>57927</v>
+        <v>57835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -927,14 +927,10 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1006,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132110040</v>
+        <v>132110059</v>
       </c>
       <c r="B5" t="n">
-        <v>57835</v>
+        <v>57927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,16 +1013,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1040,10 +1036,14 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>132110046</v>
       </c>
       <c r="B3" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132110059</v>
       </c>
       <c r="B4" t="n">
-        <v>57927</v>
+        <v>57961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>132110040</v>
       </c>
       <c r="B5" t="n">
-        <v>57835</v>
+        <v>57869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>132110046</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132110040</v>
       </c>
       <c r="B4" t="n">
-        <v>57869</v>
+        <v>57870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>132110059</v>
       </c>
       <c r="B5" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>132110046</v>
       </c>
       <c r="B3" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132110040</v>
+        <v>132110059</v>
       </c>
       <c r="B4" t="n">
-        <v>57870</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -927,10 +927,14 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1002,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132110059</v>
+        <v>132110040</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57874</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,16 +1017,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1036,14 +1040,10 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132110059</v>
+        <v>132110040</v>
       </c>
       <c r="B4" t="n">
-        <v>57966</v>
+        <v>57874</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -927,14 +927,10 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1006,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132110040</v>
+        <v>132110059</v>
       </c>
       <c r="B5" t="n">
-        <v>57874</v>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,16 +1013,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1040,10 +1036,14 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>132110046</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>132110040</v>
       </c>
       <c r="B4" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>132110059</v>
       </c>
       <c r="B5" t="n">
-        <v>57966</v>
+        <v>57967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15988-2025 artfynd.xlsx
+++ b/artfynd/A 15988-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126301609</v>
+        <v>132110040</v>
       </c>
       <c r="B2" t="n">
-        <v>57646</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102119</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -712,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363628</v>
+        <v>363552</v>
       </c>
       <c r="R2" t="n">
-        <v>6612927</v>
+        <v>6612912</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132110046</v>
+        <v>132110059</v>
       </c>
       <c r="B3" t="n">
-        <v>57951</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -814,14 +814,18 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -893,27 +897,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132110040</v>
+        <v>132110046</v>
       </c>
       <c r="B4" t="n">
-        <v>57875</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -923,14 +927,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1002,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132110059</v>
+        <v>126301609</v>
       </c>
       <c r="B5" t="n">
-        <v>57967</v>
+        <v>57942</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>102119</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1036,14 +1040,10 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363552</v>
+        <v>363628</v>
       </c>
       <c r="R5" t="n">
-        <v>6612912</v>
+        <v>6612927</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
